--- a/Equivalence Partitioning Test Cases.xlsx
+++ b/Equivalence Partitioning Test Cases.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30516"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E484E5E5-C0C8-4746-8269-870940496FE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{888F14F1-109A-4A99-A475-C972F3A08DEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="62">
   <si>
     <t xml:space="preserve">  Marks Input</t>
   </si>
@@ -181,6 +181,48 @@
   </si>
   <si>
     <t>More than 6 tickets</t>
+  </si>
+  <si>
+    <t>Requirement for the application</t>
+  </si>
+  <si>
+    <t>Input Matrix</t>
+  </si>
+  <si>
+    <t>Matrix Type</t>
+  </si>
+  <si>
+    <t>Eigenvalues</t>
+  </si>
+  <si>
+    <t>Diagonalizable</t>
+  </si>
+  <si>
+    <t>Matrix D</t>
+  </si>
+  <si>
+    <t>Expected Output</t>
+  </si>
+  <si>
+    <t>2 1 0 0 
+0 5 2 0
+0 0 7 3
+0 0 0 9</t>
+  </si>
+  <si>
+    <t>4×4 Square Matrix</t>
+  </si>
+  <si>
+    <t>2, 5, 7, 9</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>Diagonal matrix with 2, 5, 7, 9</t>
+  </si>
+  <si>
+    <t>Display P and D such that A = PDP⁻¹</t>
   </si>
 </sst>
 </file>
@@ -442,7 +484,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -514,6 +556,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -532,6 +577,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -846,15 +898,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I54"/>
+  <dimension ref="A1:J58"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10.5703125" customWidth="1"/>
-    <col min="2" max="2" width="17.7109375" customWidth="1"/>
+    <col min="1" max="1" width="12.85546875" customWidth="1"/>
+    <col min="2" max="2" width="28.85546875" customWidth="1"/>
     <col min="3" max="3" width="10.42578125" customWidth="1"/>
     <col min="4" max="4" width="20.7109375" customWidth="1"/>
     <col min="5" max="5" width="17.85546875" customWidth="1"/>
-    <col min="6" max="6" width="14.140625" customWidth="1"/>
+    <col min="6" max="6" width="32.28515625" customWidth="1"/>
+    <col min="7" max="7" width="31.7109375" customWidth="1"/>
+    <col min="9" max="10" width="39.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -1490,22 +1544,22 @@
       </c>
     </row>
     <row r="42" spans="1:6">
-      <c r="A42" s="27" t="s">
+      <c r="A42" s="28" t="s">
         <v>41</v>
       </c>
-      <c r="B42" s="28"/>
-      <c r="C42" s="28"/>
-      <c r="D42" s="28"/>
-      <c r="E42" s="28"/>
-      <c r="F42" s="29"/>
+      <c r="B42" s="29"/>
+      <c r="C42" s="29"/>
+      <c r="D42" s="29"/>
+      <c r="E42" s="29"/>
+      <c r="F42" s="30"/>
     </row>
     <row r="43" spans="1:6">
-      <c r="A43" s="30"/>
-      <c r="B43" s="31"/>
-      <c r="C43" s="31"/>
-      <c r="D43" s="31"/>
-      <c r="E43" s="31"/>
-      <c r="F43" s="32"/>
+      <c r="A43" s="31"/>
+      <c r="B43" s="32"/>
+      <c r="C43" s="32"/>
+      <c r="D43" s="32"/>
+      <c r="E43" s="32"/>
+      <c r="F43" s="33"/>
     </row>
     <row r="44" spans="1:6">
       <c r="A44" s="2" t="s">
@@ -1588,24 +1642,24 @@
       </c>
     </row>
     <row r="48" spans="1:6">
-      <c r="A48" s="27" t="s">
+      <c r="A48" s="28" t="s">
         <v>45</v>
       </c>
-      <c r="B48" s="28"/>
-      <c r="C48" s="28"/>
-      <c r="D48" s="28"/>
-      <c r="E48" s="28"/>
-      <c r="F48" s="29"/>
-    </row>
-    <row r="49" spans="1:6">
-      <c r="A49" s="30"/>
-      <c r="B49" s="31"/>
-      <c r="C49" s="31"/>
-      <c r="D49" s="31"/>
-      <c r="E49" s="31"/>
-      <c r="F49" s="32"/>
-    </row>
-    <row r="50" spans="1:6">
+      <c r="B48" s="29"/>
+      <c r="C48" s="29"/>
+      <c r="D48" s="29"/>
+      <c r="E48" s="29"/>
+      <c r="F48" s="30"/>
+    </row>
+    <row r="49" spans="1:10">
+      <c r="A49" s="31"/>
+      <c r="B49" s="32"/>
+      <c r="C49" s="32"/>
+      <c r="D49" s="32"/>
+      <c r="E49" s="32"/>
+      <c r="F49" s="33"/>
+    </row>
+    <row r="50" spans="1:10">
       <c r="A50" s="6" t="s">
         <v>1</v>
       </c>
@@ -1625,7 +1679,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="51" spans="1:6">
+    <row r="51" spans="1:10">
       <c r="A51" s="5">
         <v>1</v>
       </c>
@@ -1645,7 +1699,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="52" spans="1:6">
+    <row r="52" spans="1:10">
       <c r="A52" s="5">
         <v>2</v>
       </c>
@@ -1665,7 +1719,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="53" spans="1:6">
+    <row r="53" spans="1:10">
       <c r="A53" s="5">
         <v>3</v>
       </c>
@@ -1685,18 +1739,92 @@
         <v>13</v>
       </c>
     </row>
-    <row r="54" spans="1:6">
-      <c r="A54" s="5"/>
-      <c r="B54" s="5"/>
-      <c r="C54" s="5"/>
-      <c r="D54" s="5"/>
-      <c r="E54" s="5"/>
-      <c r="F54" s="5"/>
+    <row r="54" spans="1:10">
+      <c r="A54" s="36"/>
+      <c r="B54" s="36"/>
+      <c r="C54" s="36"/>
+      <c r="D54" s="36"/>
+      <c r="E54" s="36"/>
+      <c r="F54" s="36"/>
+    </row>
+    <row r="55" spans="1:10">
+      <c r="A55" s="27" t="s">
+        <v>49</v>
+      </c>
+      <c r="B55" s="27"/>
+      <c r="C55" s="27"/>
+      <c r="D55" s="27"/>
+      <c r="E55" s="27"/>
+      <c r="F55" s="27"/>
+      <c r="G55" s="5"/>
+      <c r="H55" s="5"/>
+    </row>
+    <row r="56" spans="1:10">
+      <c r="A56" s="27"/>
+      <c r="B56" s="27"/>
+      <c r="C56" s="27"/>
+      <c r="D56" s="27"/>
+      <c r="E56" s="27"/>
+      <c r="F56" s="27"/>
+      <c r="G56" s="5"/>
+      <c r="H56" s="5"/>
+    </row>
+    <row r="57" spans="1:10">
+      <c r="A57" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C57" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="D57" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="E57" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="F57" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="G57" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="H57" s="6"/>
+      <c r="I57" s="1"/>
+      <c r="J57" s="1"/>
+    </row>
+    <row r="58" spans="1:10" ht="60.75">
+      <c r="A58" s="5">
+        <v>1</v>
+      </c>
+      <c r="B58" s="35" t="s">
+        <v>56</v>
+      </c>
+      <c r="C58" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D58" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="E58" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="F58" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="G58" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="H58" s="5"/>
+      <c r="I58" s="34"/>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="10">
     <mergeCell ref="A42:F43"/>
     <mergeCell ref="A48:F49"/>
+    <mergeCell ref="A55:F56"/>
     <mergeCell ref="A36:F37"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
